--- a/reports/devops-juniors-israel-2026-W22.xlsx
+++ b/reports/devops-juniors-israel-2026-W22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-25T06:40:55</t>
+    <t xml:space="preserve">2026-05-25T10:44:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -178,526 +178,466 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAD Engineering - Student position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLSTARSIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Student, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4418693841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAD Engineering - Student position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLSTARSIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4329813196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">morning by Green Invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer</t>
@@ -721,34 +661,34 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brazil</t>
   </si>
   <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk JB-594</t>
   </si>
   <si>
     <t xml:space="preserve">PwC Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
   </si>
   <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
   </si>
   <si>
     <t xml:space="preserve">IT Helpdesk Engineer</t>
@@ -760,13 +700,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
   </si>
   <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
   </si>
   <si>
     <t xml:space="preserve">GNESS</t>
@@ -823,6 +766,18 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
     <t xml:space="preserve">AudioCodes</t>
   </si>
   <si>
@@ -835,6 +790,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
   </si>
   <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-service-desk-specialist-at-gong-4402928561</t>
+  </si>
+  <si>
     <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
   </si>
   <si>
@@ -847,24 +808,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-service-desk-specialist-at-gong-4402928561</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Specialist (Part time )</t>
   </si>
   <si>
@@ -880,10 +823,28 @@
     <t xml:space="preserve">UR Tech Jobs</t>
   </si>
   <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412660724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
   </si>
   <si>
     <t xml:space="preserve">Unity3D</t>
@@ -901,6 +862,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4413546871</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk Technician (36097)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418674486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (35746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-35746-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418664743</t>
+  </si>
+  <si>
     <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
   </si>
   <si>
@@ -910,21 +886,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418674486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (35746)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-35746-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418664743</t>
-  </si>
-  <si>
     <t xml:space="preserve">טכנאי/ת Help desk</t>
   </si>
   <si>
@@ -943,15 +904,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-rooms-by-fattal-4404692154</t>
   </si>
   <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spinomenal</t>
   </si>
   <si>
@@ -967,10 +919,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
   </si>
   <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineering Student</t>
@@ -988,124 +946,118 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/architectural-intern-and-personal-assistant-at-oberson-architects-4411144727</t>
   </si>
   <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">remoteok</t>
@@ -1233,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1241,7 +1193,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1249,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1257,7 +1209,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -1339,7 +1291,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -1347,7 +1299,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1355,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1363,7 +1315,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1389,7 +1341,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
@@ -1529,10 +1481,10 @@
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
@@ -1558,25 +1510,25 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3">
+        <v>71</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3">
-        <v>100</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -1584,31 +1536,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3">
+        <v>70</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3">
-        <v>96</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1616,31 +1568,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -1648,31 +1600,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3">
+        <v>52</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>84</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1680,31 +1632,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>52</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3">
-        <v>74</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1712,10 +1664,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>51</v>
@@ -1724,19 +1676,19 @@
         <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -1744,31 +1696,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3">
+        <v>48</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3">
-        <v>70</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -1776,31 +1728,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>94</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -1808,31 +1760,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -1840,31 +1792,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1872,28 +1824,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>48</v>
@@ -1904,31 +1856,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1936,28 +1888,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>48</v>
@@ -1968,31 +1920,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -2000,31 +1952,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -2038,25 +1990,25 @@
         <v>129</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="3">
+        <v>32</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>47</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
@@ -2064,28 +2016,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>44</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
@@ -2096,31 +2048,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="3">
+        <v>28</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="3">
-        <v>44</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -2128,28 +2080,28 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>27</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>44</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>48</v>
@@ -2160,28 +2112,28 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3">
+        <v>26</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>40</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>48</v>
@@ -2192,31 +2144,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -2224,31 +2176,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>37</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2301,7 +2253,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2316,22 +2268,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
@@ -2354,7 +2306,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2389,7 +2341,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2415,16 +2367,16 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2436,7 +2388,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2447,179 +2399,179 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>71</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3">
-        <v>100</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3">
+        <v>70</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
-        <v>96</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>84</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>74</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
@@ -2628,194 +2580,194 @@
         <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>48</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="3">
-        <v>70</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="K13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="K14" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>48</v>
@@ -2826,66 +2778,66 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>48</v>
@@ -2896,34 +2848,34 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="K18" s="3">
         <v>4</v>
@@ -2931,37 +2883,37 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2972,60 +2924,60 @@
         <v>129</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="3">
+        <v>32</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>47</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="K20" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>30</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>44</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
@@ -3036,66 +2988,66 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3">
+        <v>28</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="3">
-        <v>44</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>44</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>48</v>
@@ -3106,31 +3058,31 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="3">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>40</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>48</v>
@@ -3141,209 +3093,209 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="K25" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>23</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>37</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K26" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>23</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>36</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="K27" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>20</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>34</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="K28" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="K30" s="3">
         <v>6</v>
@@ -3354,98 +3306,98 @@
         <v>60</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>20</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="3">
-        <v>32</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="K31" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K32" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>48</v>
@@ -3456,171 +3408,171 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K34" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="K35" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="K36" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>199</v>
+        <v>113</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="K37" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="3">
-        <v>20</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>48</v>
@@ -3631,104 +3583,104 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="3">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>20</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="K39" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K40" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>17</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K41" s="3">
         <v>1</v>
@@ -3736,69 +3688,69 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>17</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="K42" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="3">
-        <v>13</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K43" s="3">
         <v>1</v>
@@ -3806,34 +3758,34 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>225</v>
+        <v>93</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>125</v>
+        <v>222</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K44" s="3">
         <v>1</v>
@@ -3841,34 +3793,34 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K45" s="3">
         <v>1</v>
@@ -3876,13 +3828,13 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3891,54 +3843,54 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>236</v>
+        <v>110</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>233</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K47" s="3">
         <v>1</v>
@@ -3946,34 +3898,34 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="G48" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="3">
-        <v>10</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="J48" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K48" s="3">
         <v>1</v>
@@ -3981,69 +3933,69 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="3">
+        <v>6</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>10</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="J50" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K50" s="3">
         <v>1</v>
@@ -4051,34 +4003,34 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>128</v>
+        <v>246</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K51" s="3">
         <v>1</v>
@@ -4086,25 +4038,25 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>66</v>
+        <v>250</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>251</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>252</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
@@ -4113,42 +4065,42 @@
         <v>253</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="3">
-        <v>8</v>
-      </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>258</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K53" s="3">
         <v>1</v>
@@ -4156,42 +4108,42 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="3">
-        <v>8</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="J54" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>261</v>
@@ -4206,19 +4158,19 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>264</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K55" s="3">
         <v>1</v>
@@ -4226,13 +4178,13 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>267</v>
+        <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4241,19 +4193,19 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K56" s="3">
         <v>1</v>
@@ -4261,60 +4213,60 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="3">
-        <v>6</v>
-      </c>
-      <c r="F57" s="3" t="s">
+      <c r="G57" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="J57" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E58" s="3">
-        <v>6</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="G58" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
@@ -4323,7 +4275,7 @@
         <v>276</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K58" s="3">
         <v>1</v>
@@ -4331,139 +4283,139 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3">
-        <v>6</v>
-      </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K59" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="3">
-        <v>6</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="G61" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>6</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="J61" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" s="3">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>289</v>
-      </c>
       <c r="J62" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K62" s="3">
         <v>1</v>
@@ -4471,13 +4423,13 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4486,33 +4438,33 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>94</v>
+        <v>291</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>73</v>
+        <v>292</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4521,19 +4473,19 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K64" s="3">
         <v>1</v>
@@ -4541,13 +4493,13 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>169</v>
+        <v>93</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4556,33 +4508,33 @@
         <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>298</v>
+        <v>163</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>125</v>
+        <v>296</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>73</v>
+        <v>297</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
@@ -4591,33 +4543,33 @@
         <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>301</v>
+        <v>163</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>125</v>
+        <v>299</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4626,19 +4578,19 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K67" s="3">
         <v>1</v>
@@ -4646,13 +4598,13 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>303</v>
+        <v>43</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>305</v>
+        <v>51</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4661,33 +4613,33 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K68" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4696,265 +4648,92 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>86</v>
+        <v>305</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>309</v>
+        <v>192</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>310</v>
+        <v>74</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>291</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>235</v>
+        <v>307</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>313</v>
+        <v>202</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>291</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K71" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K72" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K73" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" s="3">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E75" s="3">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K75" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K76" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K76"/>
+  <autoFilter ref="A1:K71"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5026,11 +4805,6 @@
     <hyperlink ref="I69" r:id="rId68"/>
     <hyperlink ref="I70" r:id="rId69"/>
     <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5038,8 +4812,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="53" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -5061,10 +4835,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -5072,102 +4846,102 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -5176,21 +4950,21 @@
         <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -5199,21 +4973,21 @@
         <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -5222,44 +4996,44 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -5268,38 +5042,107 @@
         <v>3</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>319</v>
+        <v>120</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>59</v>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5311,6 +5154,9 @@
     <hyperlink ref="F9" r:id="rId8"/>
     <hyperlink ref="F10" r:id="rId9"/>
     <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
+    <hyperlink ref="F14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5325,178 +5171,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="B4" s="3">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>337</v>
+        <v>194</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>223</v>
+        <v>322</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>342</v>
+        <v>275</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -5516,10 +5362,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2">
@@ -5527,10 +5373,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3">
@@ -5538,10 +5384,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4">
@@ -5549,10 +5395,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
@@ -5560,10 +5406,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6">
@@ -5574,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -5595,13 +5441,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
@@ -5612,7 +5458,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5621,22 +5467,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W22.xlsx
+++ b/reports/devops-juniors-israel-2026-W22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="378">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-25T10:44:35</t>
+    <t xml:space="preserve">2026-05-26T10:17:09</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -178,6 +178,69 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Student</t>
   </si>
   <si>
@@ -193,9 +256,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
@@ -220,6 +280,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -247,6 +331,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
   </si>
   <si>
+    <t xml:space="preserve">QA Student, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4419112669</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAP ECC System Administrator</t>
   </si>
   <si>
@@ -283,9 +382,6 @@
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -310,6 +406,36 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Technical Support</t>
   </si>
   <si>
@@ -346,9 +472,6 @@
     <t xml:space="preserve">Cato Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -367,6 +490,42 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
   </si>
   <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
   </si>
   <si>
@@ -376,6 +535,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
     <t xml:space="preserve">Information Technology Help Desk</t>
   </si>
   <si>
@@ -400,9 +571,6 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
     <t xml:space="preserve">Menora Mivtachim Group</t>
   </si>
   <si>
@@ -412,57 +580,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 2 Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
   </si>
   <si>
     <t xml:space="preserve">Network Operations Center Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-engineer-at-extreme-4416668921</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
-  </si>
-  <si>
     <t xml:space="preserve">AI Bootcamp Course 2</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Git</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -487,505 +631,457 @@
     <t xml:space="preserve">2026-05-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLSTARSIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4412906510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4413869359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4671830006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-service-desk-specialist-at-gong-4402928561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4408229150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (36097)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418674486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLSTARSIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">morning by Green Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4412906510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4413869359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4671830006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-service-desk-specialist-at-gong-4402928561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4408229150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412660724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4413546871</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418674486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (35746)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-35746-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418664743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architectural intern and personal assistant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oberson Architects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/architectural-intern-and-personal-assistant-at-oberson-architects-4411144727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROOMS by Fattal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-rooms-by-fattal-4404692154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architectural intern and personal assistant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oberson Architects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/architectural-intern-and-personal-assistant-at-oberson-architects-4411144727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -994,21 +1090,18 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
@@ -1019,12 +1112,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1185,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -1193,7 +1280,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1201,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1209,7 +1296,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -1291,7 +1378,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -1299,7 +1386,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1307,7 +1394,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1341,7 +1428,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
@@ -1481,10 +1568,10 @@
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
@@ -1510,25 +1597,25 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1536,31 +1623,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3">
-        <v>70</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1568,31 +1655,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -1600,28 +1687,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>59</v>
@@ -1632,28 +1719,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>48</v>
@@ -1664,31 +1751,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -1696,31 +1783,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -1728,31 +1815,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3">
+        <v>60</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>47</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -1760,28 +1847,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="3">
+        <v>57</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
@@ -1792,31 +1879,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -1824,31 +1911,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="3">
+        <v>52</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
@@ -1856,28 +1943,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3">
+        <v>52</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>40</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
@@ -1888,10 +1975,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>51</v>
@@ -1900,19 +1987,19 @@
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -1926,25 +2013,25 @@
         <v>121</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3">
+        <v>48</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>34</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -1955,28 +2042,28 @@
         <v>125</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1984,31 +2071,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2016,28 +2103,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
@@ -2048,31 +2135,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2080,31 +2167,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24">
@@ -2112,28 +2199,28 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>48</v>
@@ -2144,28 +2231,28 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>48</v>
@@ -2176,31 +2263,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2253,7 +2340,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2268,22 +2355,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2">
@@ -2306,7 +2393,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2318,7 +2405,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2341,7 +2428,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2353,7 +2440,7 @@
         <v>48</v>
       </c>
       <c r="K3" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2367,16 +2454,16 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2388,7 +2475,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2399,424 +2486,424 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>84</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3">
-        <v>70</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="K7" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="K10" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="3">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>47</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K12" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3">
+        <v>57</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3">
+        <v>52</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="K15" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3">
+        <v>52</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>40</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K16" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>51</v>
@@ -2825,25 +2912,25 @@
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K17" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -2854,31 +2941,31 @@
         <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <v>48</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>34</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="K18" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2886,340 +2973,340 @@
         <v>125</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="K20" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K21" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="K22" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="K23" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K24" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="K27" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>172</v>
@@ -3228,7 +3315,7 @@
         <v>48</v>
       </c>
       <c r="K28" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -3239,159 +3326,159 @@
         <v>174</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>36</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>20</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K29" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K30" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>183</v>
+        <v>60</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>32</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>17</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K32" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>186</v>
+        <v>54</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
@@ -3400,10 +3487,10 @@
         <v>190</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K33" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -3411,162 +3498,162 @@
         <v>191</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>28</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="3">
-        <v>13</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>192</v>
+        <v>88</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E35" s="3">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K36" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>23</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
@@ -3575,10 +3662,10 @@
         <v>207</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="K38" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3586,241 +3673,241 @@
         <v>208</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K39" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K40" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K41" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>113</v>
+        <v>221</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="K42" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>93</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>51</v>
+        <v>228</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K44" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="K45" s="3">
         <v>1</v>
@@ -3828,270 +3915,270 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>229</v>
+        <v>121</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>128</v>
+        <v>237</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K47" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>237</v>
+        <v>102</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E48" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>79</v>
+        <v>245</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>248</v>
+        <v>132</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K51" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>250</v>
+        <v>154</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>251</v>
+        <v>88</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>252</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>255</v>
+        <v>62</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>256</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
@@ -4100,15 +4187,15 @@
         <v>257</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>258</v>
@@ -4120,48 +4207,48 @@
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K54" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>261</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="3">
+        <v>8</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>6</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="G55" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
@@ -4173,7 +4260,7 @@
         <v>59</v>
       </c>
       <c r="K55" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -4184,168 +4271,168 @@
         <v>265</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>51</v>
+        <v>266</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K56" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F57" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="J57" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="G58" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K58" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="K60" s="3">
         <v>1</v>
@@ -4353,104 +4440,104 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>282</v>
+        <v>154</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>88</v>
+        <v>283</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>278</v>
-      </c>
       <c r="G62" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K62" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>120</v>
+        <v>291</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>110</v>
+        <v>293</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="K63" s="3">
         <v>0</v>
@@ -4458,34 +4545,34 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>290</v>
+        <v>213</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>292</v>
+        <v>51</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E64" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="K64" s="3">
         <v>1</v>
@@ -4493,142 +4580,142 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>93</v>
+        <v>297</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>163</v>
+        <v>300</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>297</v>
+        <v>56</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="K66" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>163</v>
+        <v>303</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K67" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>51</v>
+        <v>309</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K68" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4636,10 +4723,10 @@
         <v>43</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>51</v>
+        <v>277</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4648,92 +4735,374 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K69" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>192</v>
+        <v>121</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="G70" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K72" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K73" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K74" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K75" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K76" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K77" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="3">
+        <v>3</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K78" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E79" s="3">
         <v>0</v>
       </c>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="J71" s="3" t="s">
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J79" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K71" s="3">
-        <v>1</v>
+      <c r="K79" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K71"/>
+  <autoFilter ref="A1:K79"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4805,6 +5174,14 @@
     <hyperlink ref="I69" r:id="rId68"/>
     <hyperlink ref="I70" r:id="rId69"/>
     <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
+    <hyperlink ref="I79" r:id="rId78"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4812,8 +5189,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="53" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4835,10 +5212,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4846,125 +5223,125 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>203</v>
+        <v>256</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>231</v>
+        <v>294</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>251</v>
+        <v>301</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -4973,176 +5350,40 @@
         <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>318</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>244</v>
+        <v>320</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>259</v>
+        <v>321</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5151,12 +5392,6 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
-    <hyperlink ref="F14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5171,178 +5406,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -5362,10 +5597,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5373,10 +5608,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3">
@@ -5384,10 +5619,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -5395,10 +5630,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5">
@@ -5409,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6">
@@ -5420,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -5441,13 +5676,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
@@ -5458,7 +5693,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5467,22 +5702,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W22.xlsx
+++ b/reports/devops-juniors-israel-2026-W22.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-26T10:17:09</t>
+    <t xml:space="preserve">2026-05-27T10:16:41</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -214,21 +214,6 @@
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux System Engineer</t>
   </si>
   <si>
@@ -256,459 +241,420 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAD Engineering - Student position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Student, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4419112669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAD Engineering - Student position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLSTARSIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLSTARSIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
@@ -718,13 +664,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
+    <t xml:space="preserve">morning by Green Invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
@@ -733,9 +679,6 @@
     <t xml:space="preserve">Intezer</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
   </si>
   <si>
@@ -745,6 +688,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4412906510</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Data Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8541781002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -766,21 +727,21 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk JB-594</t>
   </si>
   <si>
     <t xml:space="preserve">PwC Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
-  </si>
-  <si>
     <t xml:space="preserve">Partner</t>
   </si>
   <si>
@@ -799,313 +760,352 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-dialog-4418557619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4671830006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4408229150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - SiPh Test Solutions (Teradyne, Haifa, Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teradyne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-siph-test-solutions-teradyne-haifa-israel-at-teradyne-4416856875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4413546871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (36097)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418674486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (35746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-35746-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418664743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">GNESS</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4413869359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4671830006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-service-desk-specialist-at-gong-4402928561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4408229150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418674486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architectural intern and personal assistant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oberson Architects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/architectural-intern-and-personal-assistant-at-oberson-architects-4411144727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4413546871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architectural intern and personal assistant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oberson Architects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/architectural-intern-and-personal-assistant-at-oberson-architects-4411144727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -1272,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1280,7 +1280,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1296,7 +1296,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -1378,7 +1378,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -1394,7 +1394,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1428,7 +1428,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1436,7 +1436,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1626,28 +1626,28 @@
         <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -1655,31 +1655,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1693,22 +1693,22 @@
         <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>59</v>
@@ -1719,31 +1719,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>64</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>71</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -1751,31 +1751,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3">
+        <v>60</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="3">
-        <v>70</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -1783,19 +1783,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F11" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>89</v>
@@ -1807,7 +1807,7 @@
         <v>90</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -1824,10 +1824,10 @@
         <v>93</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>94</v>
@@ -1839,7 +1839,7 @@
         <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -1853,22 +1853,22 @@
         <v>97</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
@@ -1879,19 +1879,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>103</v>
@@ -1903,7 +1903,7 @@
         <v>104</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15">
@@ -1911,31 +1911,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1943,28 +1943,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
@@ -1975,31 +1975,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -2007,31 +2007,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="19">
@@ -2039,31 +2039,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20">
@@ -2071,19 +2071,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>133</v>
@@ -2106,25 +2106,25 @@
         <v>135</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>37</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>47</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
@@ -2135,28 +2135,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="3">
+        <v>36</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>44</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>48</v>
@@ -2167,31 +2167,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>34</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3">
-        <v>44</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="24">
@@ -2199,31 +2199,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>34</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>44</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -2231,31 +2231,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -2263,31 +2263,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2340,7 +2340,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2355,22 +2355,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
@@ -2393,7 +2393,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2405,7 +2405,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2428,7 +2428,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2440,7 +2440,7 @@
         <v>48</v>
       </c>
       <c r="K3" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2463,7 +2463,7 @@
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2475,7 +2475,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2498,7 +2498,7 @@
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2510,7 +2510,7 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2518,69 +2518,69 @@
         <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K6" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2591,124 +2591,124 @@
         <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>71</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K9" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3">
-        <v>70</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K10" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -2717,10 +2717,10 @@
         <v>90</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="K11" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -2734,16 +2734,16 @@
         <v>93</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
@@ -2752,10 +2752,10 @@
         <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K12" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -2766,54 +2766,54 @@
         <v>97</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2822,7 +2822,7 @@
         <v>104</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K14" s="3">
         <v>2</v>
@@ -2830,200 +2830,200 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K16" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="K17" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
+        <v>44</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="K19" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>133</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
@@ -3035,7 +3035,7 @@
         <v>48</v>
       </c>
       <c r="K20" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -3043,512 +3043,512 @@
         <v>135</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>37</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>47</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K21" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3">
+        <v>36</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>44</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K22" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>34</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="3">
-        <v>44</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K23" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>34</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>44</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K24" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K25" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="K26" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K27" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K28" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K29" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>23</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>34</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="K30" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>180</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="K31" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="3">
+        <v>20</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="K32" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>62</v>
+        <v>189</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="K33" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="K34" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
@@ -3560,249 +3560,249 @@
         <v>48</v>
       </c>
       <c r="K35" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>88</v>
+        <v>198</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>62</v>
+        <v>199</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K36" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="K37" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="3">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="3">
-        <v>23</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="G38" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="3">
-        <v>20</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K39" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>13</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>20</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="K40" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>13</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>20</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K41" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>13</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>20</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="K42" s="3">
         <v>7</v>
@@ -3810,133 +3810,133 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="3">
+        <v>12</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>17</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="G44" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="3">
-        <v>13</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>231</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>234</v>
+        <v>111</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>236</v>
@@ -3945,88 +3945,88 @@
         <v>59</v>
       </c>
       <c r="K46" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="G47" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>13</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K47" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="3">
-        <v>12</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K48" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>245</v>
+        <v>62</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4035,33 +4035,33 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>248</v>
+        <v>51</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4073,30 +4073,30 @@
         <v>246</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K50" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4105,33 +4105,33 @@
         <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K51" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>154</v>
+        <v>251</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>88</v>
+        <v>252</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>62</v>
+        <v>253</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4140,10 +4140,10 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
@@ -4152,7 +4152,7 @@
         <v>254</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K52" s="3">
         <v>2</v>
@@ -4160,13 +4160,13 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>255</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>62</v>
+        <v>256</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4175,10 +4175,10 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
@@ -4187,7 +4187,7 @@
         <v>257</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="K53" s="3">
         <v>0</v>
@@ -4195,48 +4195,48 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>125</v>
+        <v>258</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>51</v>
+        <v>260</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K54" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>26</v>
@@ -4245,27 +4245,27 @@
         <v>8</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K55" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>264</v>
+        <v>187</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>265</v>
@@ -4274,19 +4274,19 @@
         <v>266</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>267</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>268</v>
@@ -4295,53 +4295,53 @@
         <v>59</v>
       </c>
       <c r="K56" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>110</v>
+        <v>269</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>267</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K57" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4350,33 +4350,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="K58" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4385,33 +4385,33 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K59" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>279</v>
+        <v>212</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>51</v>
+        <v>284</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4423,30 +4423,30 @@
         <v>281</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="K60" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4455,33 +4455,33 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K61" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>289</v>
+        <v>51</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4490,19 +4490,19 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K62" s="3">
         <v>2</v>
@@ -4510,13 +4510,13 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>293</v>
+        <v>51</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4525,138 +4525,138 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>213</v>
+        <v>297</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E64" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="K64" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>297</v>
+        <v>222</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>51</v>
+        <v>302</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E65" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="K65" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>56</v>
+        <v>307</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>51</v>
+        <v>253</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>26</v>
@@ -4665,68 +4665,68 @@
         <v>4</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="K67" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>312</v>
+        <v>79</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>277</v>
+        <v>62</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4735,30 +4735,30 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K69" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>62</v>
@@ -4770,33 +4770,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="K70" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>319</v>
+        <v>102</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4805,33 +4805,33 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="J71" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K71" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>323</v>
+        <v>113</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4840,19 +4840,19 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K72" s="3">
         <v>2</v>
@@ -4860,13 +4860,13 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>237</v>
+        <v>324</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>88</v>
+        <v>325</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>62</v>
+        <v>326</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4875,33 +4875,33 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K73" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>25</v>
@@ -4910,33 +4910,33 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K74" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>130</v>
+        <v>331</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>132</v>
+        <v>333</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>25</v>
@@ -4945,54 +4945,52 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="K75" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>130</v>
+        <v>335</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>331</v>
+        <v>203</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E76" s="3">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>305</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K76" s="3">
         <v>2</v>
@@ -5000,109 +4998,39 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>43</v>
+        <v>337</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E77" s="3">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K77" s="3">
         <v>3</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K77" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E78" s="3">
-        <v>3</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K78" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E79" s="3">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K79" s="3">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K79"/>
+  <autoFilter ref="A1:K77"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5180,8 +5108,6 @@
     <hyperlink ref="I75" r:id="rId74"/>
     <hyperlink ref="I76" r:id="rId75"/>
     <hyperlink ref="I77" r:id="rId76"/>
-    <hyperlink ref="I78" r:id="rId77"/>
-    <hyperlink ref="I79" r:id="rId78"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5189,11 +5115,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -5212,10 +5138,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -5223,167 +5149,144 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>61</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>255</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>109</v>
+        <v>257</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>207</v>
+        <v>277</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5391,7 +5294,6 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5417,10 +5319,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B2" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>343</v>
@@ -5428,10 +5330,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>344</v>
@@ -5439,21 +5341,21 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="3">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="B4" s="3">
-        <v>30</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>347</v>
@@ -5461,32 +5363,32 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="3">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="B6" s="3">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>256</v>
+        <v>350</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>351</v>
@@ -5494,32 +5396,32 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>355</v>
@@ -5530,7 +5432,7 @@
         <v>356</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>357</v>
@@ -5541,7 +5443,7 @@
         <v>358</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>359</v>
@@ -5552,7 +5454,7 @@
         <v>360</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>361</v>
@@ -5563,7 +5465,7 @@
         <v>362</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>363</v>
@@ -5574,7 +5476,7 @@
         <v>364</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>365</v>
@@ -5608,7 +5510,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>368</v>
@@ -5630,7 +5532,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>370</v>
@@ -5690,7 +5592,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>376</v>
@@ -5702,7 +5604,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>376</v>

--- a/reports/devops-juniors-israel-2026-W22.xlsx
+++ b/reports/devops-juniors-israel-2026-W22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-27T10:16:41</t>
+    <t xml:space="preserve">2026-05-28T10:23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -178,486 +178,456 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36311)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAD Engineering - Student position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cad-engineering-student-position-at-hillcrest-labs-acquired-by-ceva-4412295241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2 Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLSTARSIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -688,108 +658,99 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4412906510</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Data Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8541781002</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-dialog-4418557619</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-dialog-4418557619</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
   </si>
   <si>
@@ -811,27 +772,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
   </si>
   <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4671830006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
   </si>
   <si>
@@ -865,6 +817,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
     <t xml:space="preserve">AudioCodes</t>
   </si>
   <si>
@@ -874,28 +850,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
   </si>
   <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-service-desk-specialist-at-gong-4402928561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist (Part time )</t>
@@ -907,6 +874,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4408229150</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
   </si>
   <si>
@@ -925,9 +904,6 @@
     <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
   </si>
   <si>
@@ -955,15 +931,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-siph-test-solutions-teradyne-haifa-israel-at-teradyne-4416856875</t>
   </si>
   <si>
-    <t xml:space="preserve">Unity3D</t>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4417601752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Frequency System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
   </si>
   <si>
     <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4413546871</t>
-  </si>
-  <si>
     <t xml:space="preserve">Help Desk Technician (36097)</t>
   </si>
   <si>
@@ -1021,6 +1012,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineering Student</t>
   </si>
   <si>
@@ -1063,18 +1060,18 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
@@ -1096,22 +1093,22 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1272,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -1280,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1288,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1296,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -1378,7 +1375,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -1386,7 +1383,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1394,7 +1391,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1428,7 +1425,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
@@ -1436,7 +1433,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1568,10 +1565,10 @@
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
@@ -1597,25 +1594,25 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3">
-        <v>84</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -1623,31 +1620,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="3">
+        <v>57</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3">
-        <v>80</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -1655,28 +1652,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>59</v>
@@ -1687,31 +1684,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>52</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="3">
-        <v>70</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1719,19 +1716,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>80</v>
@@ -1743,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -1751,31 +1748,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -1783,28 +1780,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>48</v>
@@ -1815,31 +1812,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -1847,28 +1844,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
@@ -1879,31 +1876,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="15">
@@ -1911,28 +1908,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>48</v>
@@ -1943,28 +1940,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
@@ -1975,28 +1972,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>40</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>47</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>48</v>
@@ -2007,28 +2004,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3">
+        <v>37</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>44</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>48</v>
@@ -2039,31 +2036,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3">
+        <v>36</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="3">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -2071,31 +2068,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>34</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>44</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
@@ -2103,31 +2100,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
@@ -2135,31 +2132,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23">
@@ -2167,31 +2164,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>30</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>34</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>147</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -2199,19 +2196,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>145</v>
@@ -2220,10 +2217,10 @@
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25">
@@ -2231,31 +2228,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="3">
+        <v>26</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="3">
-        <v>32</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -2263,31 +2260,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2340,7 +2337,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2355,22 +2352,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
@@ -2393,7 +2390,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2405,7 +2402,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2428,7 +2425,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2440,7 +2437,7 @@
         <v>48</v>
       </c>
       <c r="K3" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2454,16 +2451,16 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2475,7 +2472,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2486,159 +2483,159 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3">
+        <v>70</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3">
-        <v>84</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K5" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3">
+        <v>57</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
-        <v>80</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="3">
-        <v>70</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2647,7 +2644,7 @@
         <v>81</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="K9" s="3">
         <v>7</v>
@@ -2655,524 +2652,524 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="K10" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K12" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K13" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
+        <v>44</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K14" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K16" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>40</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>47</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K17" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>37</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>44</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K18" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
+        <v>36</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="3">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>34</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>44</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="K20" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="K21" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="K22" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>30</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>34</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>147</v>
+        <v>48</v>
       </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>145</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K24" s="3">
         <v>8</v>
@@ -3180,130 +3177,130 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="3">
-        <v>32</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="K25" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="K26" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>23</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>30</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K27" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
@@ -3312,150 +3309,150 @@
         <v>169</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="K28" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K29" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="K30" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="K31" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>186</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K32" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -3469,19 +3466,19 @@
         <v>189</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>190</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>191</v>
@@ -3490,7 +3487,7 @@
         <v>48</v>
       </c>
       <c r="K33" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -3498,92 +3495,92 @@
         <v>192</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>194</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="K34" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="3">
+        <v>13</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>20</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="K35" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>200</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
@@ -3592,42 +3589,42 @@
         <v>201</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K36" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="K37" s="3">
         <v>3</v>
@@ -3635,25 +3632,25 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
@@ -3662,10 +3659,10 @@
         <v>208</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="K38" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
@@ -3673,10 +3670,10 @@
         <v>209</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3685,10 +3682,10 @@
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
@@ -3697,10 +3694,10 @@
         <v>211</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="K39" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -3708,150 +3705,150 @@
         <v>212</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>12</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>13</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="K40" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>217</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>218</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K41" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>13</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K42" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K43" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>224</v>
+        <v>113</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>226</v>
+        <v>85</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3860,33 +3857,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>232</v>
+        <v>56</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3895,33 +3892,33 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="K45" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3930,33 +3927,33 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K46" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>89</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3965,33 +3962,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K47" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4000,19 +3997,19 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="K48" s="3">
         <v>3</v>
@@ -4020,13 +4017,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4035,19 +4032,19 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="K49" s="3">
         <v>1</v>
@@ -4055,209 +4052,209 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>51</v>
+        <v>247</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K50" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="3">
+        <v>8</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>10</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="G51" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K51" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="K52" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="K54" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="K55" s="3">
         <v>3</v>
@@ -4265,13 +4262,13 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4280,33 +4277,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K56" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>269</v>
+        <v>113</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4315,33 +4312,33 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K57" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>273</v>
+        <v>176</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>275</v>
+        <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4350,33 +4347,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>280</v>
+        <v>203</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4385,10 +4382,10 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
@@ -4397,21 +4394,21 @@
         <v>282</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="K59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>284</v>
+        <v>51</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4420,10 +4417,10 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
@@ -4435,7 +4432,7 @@
         <v>59</v>
       </c>
       <c r="K60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -4446,31 +4443,31 @@
         <v>287</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>6</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="G61" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>289</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="K61" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4484,16 +4481,16 @@
         <v>51</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E62" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>292</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
@@ -4502,33 +4499,33 @@
         <v>293</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="K62" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D63" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E63" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
@@ -4537,10 +4534,10 @@
         <v>296</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>59</v>
+        <v>244</v>
       </c>
       <c r="K63" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4551,7 +4548,7 @@
         <v>298</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>51</v>
+        <v>299</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>26</v>
@@ -4560,33 +4557,33 @@
         <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K64" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>26</v>
@@ -4595,10 +4592,10 @@
         <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
@@ -4607,21 +4604,21 @@
         <v>304</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="K65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>307</v>
+        <v>51</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>26</v>
@@ -4630,33 +4627,33 @@
         <v>4</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="K66" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>253</v>
+        <v>51</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>26</v>
@@ -4665,19 +4662,19 @@
         <v>4</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K67" s="3">
         <v>0</v>
@@ -4685,48 +4682,48 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>43</v>
+        <v>309</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>271</v>
+        <v>85</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="K68" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4735,33 +4732,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K69" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4770,33 +4767,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="K70" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4805,33 +4802,33 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K71" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4840,33 +4837,33 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="K72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4875,33 +4872,33 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K73" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>25</v>
@@ -4910,33 +4907,33 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K74" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>25</v>
@@ -4945,92 +4942,162 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="K75" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>335</v>
+        <v>43</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="G76" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="K76" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>337</v>
+        <v>43</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E77" s="3">
-        <v>0</v>
-      </c>
-      <c r="F77" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="G77" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="K77" s="3">
         <v>3</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K78" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" s="3">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K79" s="3">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K77"/>
+  <autoFilter ref="A1:K79"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5108,6 +5175,8 @@
     <hyperlink ref="I75" r:id="rId74"/>
     <hyperlink ref="I76" r:id="rId75"/>
     <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
+    <hyperlink ref="I79" r:id="rId78"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5115,11 +5184,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="5" max="5" width="41" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -5138,10 +5207,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -5149,10 +5218,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
@@ -5161,67 +5230,67 @@
         <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>286</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>26</v>
@@ -5230,21 +5299,21 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>26</v>
@@ -5253,47 +5322,23 @@
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5308,76 +5353,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B5" s="3">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="B5" s="3">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>349</v>
@@ -5385,101 +5430,101 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B8" s="3">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="B8" s="3">
-        <v>21</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>322</v>
+        <v>226</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B11" s="3">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="B11" s="3">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B12" s="3">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="B12" s="3">
-        <v>10</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B13" s="3">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="B13" s="3">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="3">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="B14" s="3">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B15" s="3">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="B15" s="3">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" s="3">
+        <v>4</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="B16" s="3">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -5499,10 +5544,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5510,10 +5555,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -5521,10 +5566,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
@@ -5532,10 +5577,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
@@ -5546,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
@@ -5557,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5578,13 +5623,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="2">
@@ -5592,10 +5637,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5604,22 +5649,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W22.xlsx
+++ b/reports/devops-juniors-israel-2026-W22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-28T10:23:19</t>
+    <t xml:space="preserve">2026-05-29T10:13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,9 +100,6 @@
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
@@ -163,51 +160,117 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -265,375 +328,363 @@
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator (36311)</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4420424922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Help Desk</t>
   </si>
   <si>
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36311-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418666563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2 Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
-  </si>
-  <si>
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
     <t xml:space="preserve">morning by Green Invoice</t>
   </si>
   <si>
@@ -643,261 +694,228 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-dialog-4418557619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4412906510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-dialog-4418557619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-service-desk-specialist-at-gong-4402928561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4408229150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unilink Ltd.</t>
   </si>
   <si>
@@ -931,120 +949,114 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-siph-test-solutions-teradyne-haifa-israel-at-teradyne-4416856875</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-comblack-4420419315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4417601752</t>
   </si>
   <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Frequency System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/radio-frequency-system-engineer-at-bluebird-aero-systems-ltd-4412275099</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician (36097)</t>
+    <t xml:space="preserve">IT Support Technician (35935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-35935-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4420414750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418674486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (35746)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-35746-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418664743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architectural intern and personal assistant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oberson Architects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/architectural-intern-and-personal-assistant-at-oberson-architects-4411144727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
@@ -1057,21 +1069,21 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
@@ -1093,24 +1105,24 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -1124,9 +1136,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
@@ -1269,7 +1278,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -1277,7 +1286,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1293,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -1375,7 +1384,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -1383,7 +1392,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1391,7 +1400,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1403,36 +1412,28 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
+      <c r="B27" s="3">
+        <v>66</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="3">
         <v>11</v>
       </c>
     </row>
@@ -1445,7 +1446,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1457,34 +1458,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -1492,13 +1493,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1507,16 +1508,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -1524,31 +1525,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -1565,16 +1566,16 @@
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>58</v>
@@ -1594,25 +1595,25 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1620,31 +1621,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -1652,31 +1653,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -1684,31 +1685,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -1716,31 +1717,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -1748,31 +1749,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -1789,22 +1790,22 @@
         <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -1821,22 +1822,22 @@
         <v>96</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -1850,25 +1851,25 @@
         <v>100</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>51</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>47</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -1888,19 +1889,19 @@
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>107</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -1908,31 +1909,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1946,25 +1947,25 @@
         <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1972,31 +1973,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -2004,31 +2005,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -2036,31 +2037,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -2068,31 +2069,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
@@ -2100,31 +2101,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -2132,31 +2133,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23">
@@ -2164,31 +2165,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>34</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>30</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
@@ -2196,31 +2197,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -2228,31 +2229,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3">
+        <v>32</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3">
-        <v>26</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
@@ -2260,31 +2261,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2323,7 +2324,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2337,48 +2338,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2387,57 +2388,57 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K3" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2451,19 +2452,19 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>58</v>
@@ -2472,7 +2473,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2483,206 +2484,206 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="K6" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K7" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K8" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="K9" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -2696,28 +2697,28 @@
         <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K11" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -2731,28 +2732,28 @@
         <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K12" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -2763,31 +2764,31 @@
         <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>51</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>47</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K13" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -2804,60 +2805,60 @@
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K14" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -2868,780 +2869,780 @@
         <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K18" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K19" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="K20" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="K21" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="K22" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>34</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>30</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="K23" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="K24" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="3">
+        <v>32</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="3">
-        <v>26</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="K25" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K26" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3">
+        <v>28</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>23</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="K27" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="3">
+        <v>26</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>23</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="K28" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K29" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>48</v>
+        <v>175</v>
       </c>
       <c r="K30" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="K31" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="K32" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="3">
-        <v>16</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K33" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="3">
-        <v>13</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="K34" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="K35" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K36" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="3">
+        <v>16</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="K37" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>94</v>
+        <v>204</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3">
         <v>13</v>
@@ -3650,19 +3651,19 @@
         <v>207</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>208</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K38" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -3670,34 +3671,34 @@
         <v>209</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3">
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="K39" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -3705,66 +3706,66 @@
         <v>212</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K40" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>216</v>
+        <v>50</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="K41" s="3">
         <v>4</v>
@@ -3772,83 +3773,83 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>94</v>
+        <v>220</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K42" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>221</v>
+        <v>54</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="K43" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>113</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3857,33 +3858,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>170</v>
+        <v>53</v>
       </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>56</v>
+        <v>231</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3895,30 +3896,30 @@
         <v>229</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>231</v>
+        <v>53</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>203</v>
+        <v>110</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3927,33 +3928,33 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K46" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3962,33 +3963,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K47" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>237</v>
+        <v>170</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3997,33 +3998,33 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>88</v>
+        <v>243</v>
       </c>
       <c r="K48" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4032,68 +4033,68 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>245</v>
+        <v>54</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>59</v>
+        <v>251</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>73</v>
+        <v>252</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>26</v>
@@ -4102,68 +4103,68 @@
         <v>8</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K51" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>252</v>
+        <v>94</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K52" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4172,33 +4173,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>244</v>
+        <v>53</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4207,19 +4208,19 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="K54" s="3">
         <v>2</v>
@@ -4227,13 +4228,13 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>51</v>
+        <v>271</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4242,19 +4243,19 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K55" s="3">
         <v>3</v>
@@ -4262,13 +4263,13 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4277,19 +4278,19 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="K56" s="3">
         <v>4</v>
@@ -4297,13 +4298,13 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4312,33 +4313,33 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K57" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>51</v>
+        <v>283</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4347,33 +4348,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="K58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4382,33 +4383,33 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="K59" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4417,33 +4418,33 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K60" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>26</v>
@@ -4452,33 +4453,33 @@
         <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>26</v>
@@ -4487,33 +4488,33 @@
         <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K62" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>26</v>
@@ -4522,33 +4523,33 @@
         <v>4</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="K63" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>26</v>
@@ -4557,33 +4558,33 @@
         <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K64" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>26</v>
@@ -4592,33 +4593,33 @@
         <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="K65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>286</v>
+        <v>133</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>26</v>
@@ -4627,19 +4628,19 @@
         <v>4</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>
@@ -4647,13 +4648,13 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>26</v>
@@ -4662,33 +4663,33 @@
         <v>4</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="K67" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>26</v>
@@ -4697,33 +4698,33 @@
         <v>4</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="K68" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4732,33 +4733,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K69" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4767,33 +4768,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="K70" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>316</v>
+        <v>137</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4802,19 +4803,19 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="K71" s="3">
         <v>4</v>
@@ -4822,13 +4823,13 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>127</v>
+        <v>322</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>96</v>
+        <v>324</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4837,33 +4838,33 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="K72" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>321</v>
+        <v>54</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4872,33 +4873,33 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K73" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>326</v>
+        <v>110</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>25</v>
@@ -4907,33 +4908,33 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K74" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>328</v>
+        <v>54</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>330</v>
+        <v>77</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>25</v>
@@ -4942,33 +4943,33 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>244</v>
+        <v>53</v>
       </c>
       <c r="K75" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>43</v>
+        <v>176</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>51</v>
+        <v>334</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>25</v>
@@ -4977,33 +4978,33 @@
         <v>3</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="K76" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>43</v>
+        <v>336</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>51</v>
+        <v>338</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>25</v>
@@ -5012,33 +5013,33 @@
         <v>3</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>88</v>
+        <v>251</v>
       </c>
       <c r="K77" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>27</v>
@@ -5048,56 +5049,23 @@
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="K78" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E79" s="3">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K79" s="3">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K79"/>
+  <autoFilter ref="A1:K78"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5176,7 +5144,6 @@
     <hyperlink ref="I76" r:id="rId75"/>
     <hyperlink ref="I77" r:id="rId76"/>
     <hyperlink ref="I78" r:id="rId77"/>
-    <hyperlink ref="I79" r:id="rId78"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5184,136 +5151,136 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="41" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>228</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>286</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>288</v>
+        <v>128</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>289</v>
+        <v>129</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>286</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>288</v>
+        <v>194</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>306</v>
+        <v>195</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>309</v>
+        <v>133</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>26</v>
@@ -5322,23 +5289,47 @@
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>311</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>231</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5353,178 +5344,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B2" s="3">
         <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>351</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>348</v>
+        <v>207</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>226</v>
+        <v>320</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B10" s="3">
         <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -5541,13 +5532,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
@@ -5555,10 +5546,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
@@ -5566,10 +5557,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -5577,10 +5568,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5">
@@ -5591,18 +5582,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5620,51 +5600,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W22.xlsx
+++ b/reports/devops-juniors-israel-2026-W22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-29T10:13:58</t>
+    <t xml:space="preserve">2026-05-31T09:20:40</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -160,811 +160,763 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortinet</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst- Student position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Cloud (any), CI/CD, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8572315002?gh_jid=8572315002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-island-4408877123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4420424922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4412906510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4415205216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4418338787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
   </si>
   <si>
     <t xml:space="preserve">SAP ECC System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+    <t xml:space="preserve">SISL Global</t>
   </si>
   <si>
     <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2 Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4420424922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">morning by Green Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - SiPh Test Solutions (Teradyne, Haifa, Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teradyne</t>
   </si>
   <si>
     <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-dialog-4418557619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - SiPh Test Solutions (Teradyne, Haifa, Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teradyne</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-siph-test-solutions-teradyne-haifa-israel-at-teradyne-4416856875</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-comblack-4420419315</t>
   </si>
   <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4417601752</t>
   </si>
   <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+    <t xml:space="preserve">https://unity.com/careers/positions/7912645?gh_jid=7912645</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Technician (35935)</t>
@@ -994,6 +946,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
   </si>
   <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
     <t xml:space="preserve">Spinomenal</t>
   </si>
   <si>
@@ -1015,27 +973,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
   </si>
   <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineering Student</t>
   </si>
   <si>
@@ -1060,30 +997,30 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
@@ -1093,34 +1030,34 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1278,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1286,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1294,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1302,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -1392,7 +1329,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1400,7 +1337,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1426,7 +1363,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
@@ -1434,7 +1371,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1446,7 +1383,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1534,10 +1471,10 @@
         <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>51</v>
@@ -1566,10 +1503,10 @@
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
@@ -1581,7 +1518,7 @@
         <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -1589,31 +1526,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3">
+        <v>57</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3">
-        <v>84</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -1621,31 +1558,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>54</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3">
-        <v>80</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -1653,28 +1590,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>53</v>
@@ -1685,31 +1622,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>51</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="3">
-        <v>70</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -1717,31 +1654,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>60</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -1749,25 +1686,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>88</v>
@@ -1790,10 +1727,10 @@
         <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>92</v>
@@ -1805,7 +1742,7 @@
         <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
@@ -1822,16 +1759,16 @@
         <v>96</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>98</v>
@@ -1851,25 +1788,25 @@
         <v>100</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -1877,31 +1814,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>40</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>47</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -1909,28 +1846,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>37</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>47</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>47</v>
@@ -1941,31 +1878,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>34</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>47</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -1973,31 +1910,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>34</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>44</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -2005,31 +1942,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
@@ -2037,31 +1974,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>30</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>40</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2069,19 +2006,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>131</v>
@@ -2093,7 +2030,7 @@
         <v>132</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21">
@@ -2101,31 +2038,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
@@ -2133,31 +2070,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -2165,31 +2102,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
@@ -2197,31 +2134,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25">
@@ -2229,31 +2166,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26">
@@ -2261,31 +2198,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2338,7 +2275,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -2353,22 +2290,22 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
@@ -2391,7 +2328,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2403,7 +2340,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2417,16 +2354,16 @@
         <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2438,7 +2375,7 @@
         <v>53</v>
       </c>
       <c r="K3" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2452,16 +2389,16 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
@@ -2470,211 +2407,211 @@
         <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3">
+        <v>57</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3">
-        <v>84</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="K5" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
-        <v>80</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>53</v>
       </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>51</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="3">
-        <v>70</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3">
-        <v>60</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K9" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>88</v>
@@ -2683,7 +2620,7 @@
         <v>47</v>
       </c>
       <c r="K10" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -2697,16 +2634,16 @@
         <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
@@ -2715,10 +2652,10 @@
         <v>93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="K11" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2732,19 +2669,19 @@
         <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>98</v>
@@ -2753,7 +2690,7 @@
         <v>47</v>
       </c>
       <c r="K12" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2764,238 +2701,238 @@
         <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="K13" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>47</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="K14" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>37</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>47</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>34</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>47</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="K16" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>34</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="K17" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="K18" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>30</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>40</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K19" s="3">
         <v>0</v>
@@ -3003,25 +2940,25 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>131</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
@@ -3030,360 +2967,360 @@
         <v>132</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="K20" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="K21" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="K22" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="K23" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="K24" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="K26" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="K27" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>47</v>
       </c>
       <c r="K28" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>47</v>
       </c>
       <c r="K29" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="K30" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -3391,69 +3328,69 @@
         <v>176</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="K31" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>184</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K32" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -3464,54 +3401,54 @@
         <v>186</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>16</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="3">
-        <v>20</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="K33" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -3520,129 +3457,129 @@
         <v>192</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="K34" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="3">
+        <v>13</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>17</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="G36" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="K36" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K37" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>206</v>
+        <v>65</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
         <v>13</v>
@@ -3651,7 +3588,7 @@
         <v>207</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
@@ -3660,10 +3597,10 @@
         <v>208</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="K38" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -3671,45 +3608,45 @@
         <v>209</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>211</v>
+        <v>47</v>
       </c>
       <c r="K39" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>212</v>
+        <v>89</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3718,138 +3655,138 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="K40" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>211</v>
+        <v>53</v>
       </c>
       <c r="K41" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>13</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="K42" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K43" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>228</v>
+        <v>101</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3858,33 +3795,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>53</v>
       </c>
       <c r="K44" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3896,30 +3833,30 @@
         <v>229</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="K45" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3928,19 +3865,19 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="K46" s="3">
         <v>5</v>
@@ -3948,13 +3885,13 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3963,19 +3900,19 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>69</v>
+        <v>237</v>
       </c>
       <c r="K47" s="3">
         <v>3</v>
@@ -3983,13 +3920,13 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3998,150 +3935,150 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>10</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>211</v>
+        <v>53</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>54</v>
+        <v>245</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="3">
+        <v>8</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>10</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="J50" s="3" t="s">
-        <v>251</v>
+        <v>53</v>
       </c>
       <c r="K50" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="G51" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="3">
-        <v>8</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>53</v>
       </c>
       <c r="K51" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>94</v>
+        <v>254</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="3">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="G52" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
@@ -4150,21 +4087,21 @@
         <v>258</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>53</v>
+        <v>259</v>
       </c>
       <c r="K52" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4173,19 +4110,19 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="K53" s="3">
         <v>5</v>
@@ -4193,13 +4130,13 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>266</v>
+        <v>56</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4211,7 +4148,7 @@
         <v>267</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
@@ -4220,21 +4157,21 @@
         <v>268</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="K54" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4243,33 +4180,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="K55" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4278,33 +4215,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>211</v>
+        <v>68</v>
       </c>
       <c r="K56" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>216</v>
+        <v>274</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>279</v>
+        <v>56</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4313,138 +4250,138 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="K57" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="K58" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K59" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>69</v>
+        <v>259</v>
       </c>
       <c r="K60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>26</v>
@@ -4453,33 +4390,33 @@
         <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="K61" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>26</v>
@@ -4488,33 +4425,33 @@
         <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>53</v>
+        <v>259</v>
       </c>
       <c r="K62" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>299</v>
+        <v>143</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>300</v>
+        <v>179</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>301</v>
+        <v>130</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>26</v>
@@ -4523,19 +4460,19 @@
         <v>4</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>251</v>
+        <v>107</v>
       </c>
       <c r="K63" s="3">
         <v>2</v>
@@ -4543,13 +4480,13 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>26</v>
@@ -4558,173 +4495,173 @@
         <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="K64" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>308</v>
+        <v>42</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>251</v>
+        <v>68</v>
       </c>
       <c r="K65" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>133</v>
+        <v>301</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="K67" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>77</v>
+        <v>308</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="K68" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>261</v>
+        <v>91</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4733,33 +4670,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>53</v>
       </c>
       <c r="K69" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>317</v>
+        <v>63</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>213</v>
+        <v>312</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>62</v>
+        <v>313</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4768,33 +4705,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4803,33 +4740,33 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>211</v>
+        <v>53</v>
       </c>
       <c r="K71" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>324</v>
+        <v>56</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4838,234 +4775,59 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>53</v>
       </c>
       <c r="K72" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>54</v>
+        <v>319</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>326</v>
+        <v>194</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>327</v>
+        <v>71</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>293</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="K73" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K74" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="3">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K75" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="3">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K76" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E77" s="3">
-        <v>3</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="K77" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E78" s="3">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="K78" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K78"/>
+  <autoFilter ref="A1:K73"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5139,11 +4901,6 @@
     <hyperlink ref="I71" r:id="rId70"/>
     <hyperlink ref="I72" r:id="rId71"/>
     <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
-    <hyperlink ref="I78" r:id="rId77"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5151,9 +4908,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5174,10 +4931,10 @@
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -5185,144 +4942,236 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3">
         <v>54</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="3">
-        <v>88</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>190</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>193</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>195</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>285</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>286</v>
+        <v>124</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>272</v>
+        <v>126</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>311</v>
+        <v>138</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>317</v>
+        <v>123</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>213</v>
+        <v>152</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>59</v>
+      <c r="E11" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5330,6 +5179,10 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5344,178 +5197,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B2" s="3">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="B3" s="3">
         <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>351</v>
+        <v>196</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>207</v>
+        <v>331</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>320</v>
+        <v>232</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5535,10 +5388,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
@@ -5549,7 +5402,7 @@
         <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3">
@@ -5557,10 +5410,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4">
@@ -5568,10 +5421,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5">
@@ -5582,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -5603,13 +5456,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2">
@@ -5617,10 +5470,10 @@
         <v>31</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5629,22 +5482,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="D4" s="3"/>
     </row>
